--- a/Config/Datas/born_points.xlsx
+++ b/Config/Datas/born_points.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -116,6 +116,12 @@
   </si>
   <si>
     <t>born_newbie_03</t>
+  </si>
+  <si>
+    <t>game_init</t>
+  </si>
+  <si>
+    <t>initial_p0</t>
   </si>
 </sst>
 </file>
@@ -1049,8 +1055,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="12.25" customWidth="1"/>
     <col min="3" max="3" width="16.625" customWidth="1"/>
@@ -1158,7 +1164,6 @@
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5"/>
       <c r="G5" t="s">
         <v>22</v>
       </c>
@@ -1174,7 +1179,6 @@
       <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F6"/>
       <c r="G6" t="s">
         <v>25</v>
       </c>
@@ -1191,6 +1195,17 @@
       </c>
       <c r="G7" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
